--- a/Assets/Resources/Storys/10.xlsx
+++ b/Assets/Resources/Storys/10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10800" windowHeight="10695"/>
+    <workbookView windowWidth="21600" windowHeight="10695"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <t>不休息</t>
   </si>
   <si>
-    <t>你被抓到警察局</t>
+    <t>xiuxi</t>
   </si>
   <si>
     <t>End Of Story</t>
@@ -703,7 +703,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -712,9 +712,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1027,10 +1024,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1055,8 +1052,14 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1">
+        <v>1</v>
+      </c>
+      <c r="J1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1064,7 +1067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1080,19 +1083,17 @@
       <c r="H3">
         <v>8</v>
       </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="5" ht="27" spans="1:8">
-      <c r="B5" s="3" t="s">
-        <v>13</v>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
     </row>
